--- a/config/TeamInfo.xlsx
+++ b/config/TeamInfo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonyapc-my.sharepoint.com/personal/pranavsunil_deshmukh_sony_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkflowHub\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73763E39-C3B1-4C0F-A641-1AE5A7501B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F82279-99D9-4864-8C66-FF166867AB69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{176BDDDA-117D-4E22-A603-D179A2AC881E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{176BDDDA-117D-4E22-A603-D179A2AC881E}"/>
   </bookViews>
   <sheets>
     <sheet name="Team Info" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Employee Name</t>
   </si>
@@ -57,102 +55,6 @@
     <t>Email id</t>
   </si>
   <si>
-    <t>Ramachandran, Ramu</t>
-  </si>
-  <si>
-    <t>Ramu.Ramachandran@sony.com</t>
-  </si>
-  <si>
-    <t>Director</t>
-  </si>
-  <si>
-    <t>Associate Director</t>
-  </si>
-  <si>
-    <t>Krishna, Mohan</t>
-  </si>
-  <si>
-    <t>Mohan.Krishna@sony.com</t>
-  </si>
-  <si>
-    <t>Rajarethinam, Abilash</t>
-  </si>
-  <si>
-    <t>Senior Technical Specialist</t>
-  </si>
-  <si>
-    <t>Abilash.Rajarethinam@sony.com</t>
-  </si>
-  <si>
-    <t>Sonkar, Abhishek</t>
-  </si>
-  <si>
-    <t>Senior technical specialist</t>
-  </si>
-  <si>
-    <t>Abhishek.Sonkar@sony.com</t>
-  </si>
-  <si>
-    <t>Saurabh.Bhalgat@sony.com</t>
-  </si>
-  <si>
-    <t>Technical Specialist</t>
-  </si>
-  <si>
-    <t>Bhalgat, Saurabh</t>
-  </si>
-  <si>
-    <t>Aachman, Punya</t>
-  </si>
-  <si>
-    <t>Technical Lead</t>
-  </si>
-  <si>
-    <t>Punya.Aachman@sony.com</t>
-  </si>
-  <si>
-    <t>Baskaran, RohithNanthan</t>
-  </si>
-  <si>
-    <t>RohithNanthan.Baskaran@sony.com</t>
-  </si>
-  <si>
-    <t>G, Prajwal</t>
-  </si>
-  <si>
-    <t>Senior Software Engineer</t>
-  </si>
-  <si>
-    <t>Prajwal.G@sony.com</t>
-  </si>
-  <si>
-    <t>Krishnan, Rajesh</t>
-  </si>
-  <si>
-    <t>Rajesh.Krishnan@sony.com</t>
-  </si>
-  <si>
-    <t>Sathish.Kumar1@sony.com</t>
-  </si>
-  <si>
-    <t>Kumar, Sathish</t>
-  </si>
-  <si>
-    <t>RaoS, Sindhura</t>
-  </si>
-  <si>
-    <t>Sindhura.RaoS@sony.com</t>
-  </si>
-  <si>
-    <t>Deshmukh, PranavSunil</t>
-  </si>
-  <si>
-    <t>Consultant</t>
-  </si>
-  <si>
-    <t>PranavSunil.Deshmukh@sony.com</t>
-  </si>
-  <si>
     <t>Pods</t>
   </si>
   <si>
@@ -160,126 +62,6 @@
   </si>
   <si>
     <t>Engineers / Members</t>
-  </si>
-  <si>
-    <t>Rendering</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Rendering pipeline, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B9B62"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Shader HLSL, UnityShader Graph, Unity VFX, Unreal rendering,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> GPU-related debugging</t>
-    </r>
-  </si>
-  <si>
-    <t>Abilash, Rajesh, Saurabh, Sathish, Rohith</t>
-  </si>
-  <si>
-    <t>Gameplay / Systems</t>
-  </si>
-  <si>
-    <r>
-      <t>Module/system development</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, project-related issues, common engine/game issues, gameplay systems</t>
-    </r>
-  </si>
-  <si>
-    <t>Abhishek, Punya, Sindhura, Prajwal</t>
-  </si>
-  <si>
-    <t>Platform / PlayStation Tools</t>
-  </si>
-  <si>
-    <t>PSN, Save Data, TRC, DS Controller, platform-specific integration and compliance</t>
-  </si>
-  <si>
-    <t>Sindhura , Pranav, Rohith, Prajwal</t>
-  </si>
-  <si>
-    <t>Debugging &amp; Profiling</t>
-  </si>
-  <si>
-    <t>Debugging, profiling, performance analysis, issue investigation, SDK/tool-level debugging</t>
-  </si>
-  <si>
-    <t>Rajesh, Saurabh, Abhishek, Sindhura</t>
-  </si>
-  <si>
-    <t>CI/CD / DevOps &amp; Tools</t>
-  </si>
-  <si>
-    <r>
-      <t>Dev-utilities package</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, build/release support, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B9B62"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>automation opportunities,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> documentation, tool lifecycle support</t>
-    </r>
-  </si>
-  <si>
-    <t>Saurabh, Prajwal , Pranav, Abhishek</t>
-  </si>
-  <si>
-    <t>Audio / Middleware &amp; Haptics</t>
-  </si>
-  <si>
-    <t>FMoD, Wwise, Interhaptics, audio middleware integration, haptics support</t>
-  </si>
-  <si>
-    <t>Pranav, Saurabh</t>
   </si>
 </sst>
 </file>
@@ -683,17 +465,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BCAF135-BBE0-4F0D-A65D-563BADD15842}">
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" customWidth="1"/>
-    <col min="4" max="4" width="34.42578125" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="2" max="2" width="25.1796875" customWidth="1"/>
+    <col min="3" max="3" width="20.26953125" customWidth="1"/>
+    <col min="4" max="4" width="34.453125" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -710,146 +492,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3">
-        <v>9886719374</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13">
-        <v>7000042998</v>
-      </c>
-      <c r="D13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13">
-        <v>8149803640</v>
-      </c>
+    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.4">
+      <c r="B2" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -860,89 +504,53 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{879579C8-169C-4A03-B34B-C22C98E0FD32}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="53.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7265625" customWidth="1"/>
+    <col min="2" max="2" width="53.7265625" customWidth="1"/>
     <col min="3" max="3" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>57</v>
-      </c>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" spans="1:3" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:3" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
